--- a/andon/keywords_and_phrases_checklist.xlsx
+++ b/andon/keywords_and_phrases_checklist.xlsx
@@ -899,7 +899,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
           <t>LVP or laminate plank issues</t>
@@ -917,7 +921,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
           <t>Tile crack, lippage, layout</t>
@@ -935,7 +943,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Hardwood cupping, gaps</t>
@@ -953,7 +965,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Carpet seams, stretching</t>
@@ -971,7 +987,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Vinyl sheet or plank issues</t>
@@ -989,7 +1009,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Grout cracking, color issues</t>
@@ -1007,7 +1031,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Subfloor prep, flatness</t>
@@ -1025,7 +1053,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n"/>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Underlayment type or gaps</t>
@@ -1043,7 +1075,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Transition strip issues</t>
@@ -1061,7 +1097,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Baseboard gaps or damage</t>
@@ -1079,7 +1119,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Tile height difference</t>
@@ -1097,7 +1141,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Carpet or vinyl seam visible</t>
@@ -1115,7 +1163,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Gap between planks or at wall</t>
@@ -1133,7 +1185,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n"/>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
           <t>Floor buckling or tenting</t>
@@ -1151,7 +1207,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Floor squeaking after install</t>
@@ -1169,7 +1229,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n"/>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
           <t>Floor not level or flat</t>
@@ -1187,7 +1251,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Moisture in subfloor or slab</t>
@@ -1205,7 +1273,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n"/>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Expansion gap missing</t>
@@ -1223,7 +1295,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Glue-down issues, adhesive failure</t>
@@ -1241,7 +1317,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Carpet padding issues</t>
@@ -1259,7 +1339,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Gaps between LVP planks</t>
@@ -1277,7 +1361,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Height difference at tile edges</t>
@@ -1295,7 +1383,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Grout failing in traffic areas</t>
@@ -1313,7 +1405,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Wood absorbing moisture</t>
@@ -1331,7 +1427,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Seam shows through</t>
@@ -1349,7 +1449,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Requires self-leveler</t>
@@ -1367,7 +1471,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Missing at doorways</t>
@@ -1385,7 +1493,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Squeaks after install</t>
@@ -1403,7 +1515,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
           <t>No gap at perimeter</t>
@@ -1421,7 +1537,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Gaps at floor or wall</t>
@@ -1439,7 +1559,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Wrinkles show through flooring</t>
@@ -1457,7 +1581,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n"/>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Can't install until dry</t>
@@ -1475,7 +1603,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Cracked tile, needs replacement</t>
@@ -1493,7 +1625,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
           <t>Tile pattern not aligned</t>
@@ -1511,7 +1647,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Paint or other trades not done</t>
@@ -1529,7 +1669,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n"/>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Tent or buckle at seams</t>
@@ -1547,7 +1691,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Adhesive failure</t>
@@ -1565,7 +1713,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C39" s="18" t="n"/>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Self-leveler failed</t>
@@ -1583,7 +1735,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n"/>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Material delay from supplier</t>
@@ -1601,10 +1757,21 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C41" s="18" t="n"/>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Padding damaged during install</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -1612,6 +1779,11 @@
       <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Total entries: 40</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -1674,7 +1846,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
           <t>General cabinet issue</t>
@@ -1692,7 +1868,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
           <t>Door alignment, swing, damage</t>
@@ -1710,7 +1890,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Drawer glide, fit, front</t>
@@ -1728,7 +1912,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Hinge adjustment, damage</t>
@@ -1746,7 +1934,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Handle/pull placement or missing</t>
@@ -1764,7 +1956,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Knob location or wrong style</t>
@@ -1782,7 +1978,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Shelf adjustment, missing pins</t>
@@ -1800,7 +2000,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n"/>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Cabinet face frame alignment</t>
@@ -1818,7 +2022,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>End panel, filler, gable</t>
@@ -1836,7 +2044,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Filler strip size or gap</t>
@@ -1854,7 +2066,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Toe kick height or missing</t>
@@ -1872,7 +2088,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Crown molding alignment or gap</t>
@@ -1890,7 +2110,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Scribe piece or scribing needed</t>
@@ -1908,7 +2132,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n"/>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
           <t>Scratched finish</t>
@@ -1926,7 +2154,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Dent in cabinet body or door</t>
@@ -1944,7 +2176,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n"/>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
           <t>Cabinet not level</t>
@@ -1962,7 +2198,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Shimming visible or missing</t>
@@ -1980,7 +2220,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n"/>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Warranty replacement part needed</t>
@@ -1998,7 +2242,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Damage during delivery or install</t>
@@ -2016,7 +2264,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Door reveal uneven</t>
@@ -2034,7 +2286,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Door hitting adjacent door</t>
@@ -2052,7 +2308,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Drawer glide issue or obstruction</t>
@@ -2070,7 +2330,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Hinge damaged during install</t>
@@ -2088,7 +2352,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Gap at ceiling or cabinet top</t>
@@ -2106,7 +2374,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Toe kick height or depth off</t>
@@ -2124,7 +2396,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Gap between cabinet and wall</t>
@@ -2142,7 +2418,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Cabinet tilted or rocking</t>
@@ -2160,7 +2440,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Pulls not centered on doors</t>
@@ -2178,7 +2462,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Adjustable shelves not installed</t>
@@ -2196,7 +2484,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Visible scratch on exposed panel</t>
@@ -2214,7 +2506,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Soft-close not working</t>
@@ -2232,7 +2528,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n"/>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Door bowed or twisted</t>
@@ -2250,7 +2550,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Gap at wall, needs scribing</t>
@@ -2268,7 +2572,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
           <t>Template for counters not done</t>
@@ -2286,7 +2594,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Backsplash gap above counter</t>
@@ -2304,7 +2616,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n"/>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Island position not aligned</t>
@@ -2322,7 +2638,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Floor or walls not ready</t>
@@ -2340,7 +2660,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C39" s="18" t="n"/>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Shipping damage</t>
@@ -2358,7 +2682,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n"/>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Door hits wall or appliance</t>
@@ -2376,10 +2704,21 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C41" s="18" t="n"/>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Opening too small for appliance</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -2387,6 +2726,11 @@
       <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Total entries: 40</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -2449,7 +2793,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Base, casing, or crown issues</t>
@@ -2467,7 +2815,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
           <t>Window or door casing gaps</t>
@@ -2485,7 +2837,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Baseboard gaps or miters</t>
@@ -2503,7 +2859,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Crown molding miters or copes</t>
@@ -2521,7 +2881,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Miter joint gap or angle</t>
@@ -2539,7 +2903,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Coped joint quality</t>
@@ -2557,7 +2925,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Caulking needed or cracking</t>
@@ -2575,7 +2947,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n"/>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Nail holes, pops, or fill</t>
@@ -2593,7 +2969,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Putty not applied or color wrong</t>
@@ -2611,7 +2991,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Stain match, blotchiness</t>
@@ -2629,7 +3013,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Clear coat or polyurethane issues</t>
@@ -2647,7 +3035,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Stair tread, riser, or rail</t>
@@ -2665,7 +3057,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Railing height or loose</t>
@@ -2683,7 +3079,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n"/>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
           <t>Baluster spacing or loose</t>
@@ -2701,7 +3101,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Handrail height or brackets</t>
@@ -2719,7 +3123,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n"/>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
           <t>Column wraps or damage</t>
@@ -2737,7 +3145,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Fireplace mantel install</t>
@@ -2755,7 +3167,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n"/>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Built-in shelf or niche</t>
@@ -2773,7 +3189,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Door hardware, strike plates</t>
@@ -2791,7 +3211,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Door threshold height or gap</t>
@@ -2809,7 +3233,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Gap at corner joint</t>
@@ -2827,7 +3255,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Casing gap at jamb</t>
@@ -2845,7 +3277,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Gap under baseboard</t>
@@ -2863,7 +3299,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Crown corner not tight</t>
@@ -2881,7 +3321,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Putty not applied yet</t>
@@ -2899,7 +3343,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Caulk at trim-to-wall failed</t>
@@ -2917,7 +3365,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Touch-up stain different shade</t>
@@ -2935,7 +3387,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Railing not secured properly</t>
@@ -2953,7 +3409,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Exceeds code spacing</t>
@@ -2971,7 +3431,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Tread not glued/nailed</t>
@@ -2989,7 +3453,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Strike plate not aligned</t>
@@ -3007,7 +3475,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n"/>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Door rubbing at bottom or side</t>
@@ -3025,7 +3497,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Door seal not installed</t>
@@ -3043,7 +3519,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
           <t>Dent or scratch on column</t>
@@ -3061,7 +3541,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Fireplace surround off</t>
@@ -3079,7 +3563,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n"/>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Shelf sagging or crooked</t>
@@ -3097,7 +3585,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Wrong color/style installed</t>
@@ -3115,7 +3607,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C39" s="18" t="n"/>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Paint or other trades not done</t>
@@ -3133,7 +3629,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n"/>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Final touch-up after install</t>
@@ -3151,10 +3651,21 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C41" s="18" t="n"/>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Sill gap, not sealed</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -3162,6 +3673,11 @@
       <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Total entries: 40</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -3499,7 +4015,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Missing or wrong rebar placement</t>
@@ -3517,7 +4037,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
           <t>Form boards shifting or breaking</t>
@@ -3535,7 +4059,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Concrete pour issues, scheduling</t>
@@ -3553,7 +4081,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Concrete not curing properly</t>
@@ -3571,7 +4103,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Slab thickness, cracks, finish</t>
@@ -3589,7 +4125,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Footer depth, width, or location</t>
@@ -3607,7 +4147,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Vapor barrier missing or torn</t>
@@ -3625,7 +4169,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n"/>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Gravel base not compacted</t>
@@ -3643,7 +4191,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Grading issues around foundation</t>
@@ -3661,7 +4213,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Muddy conditions affecting pour</t>
@@ -3679,7 +4235,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Frost in ground, frost heave</t>
@@ -3697,7 +4257,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Settlement cracks or movement</t>
@@ -3715,7 +4279,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Any crack in foundation</t>
@@ -3733,7 +4301,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n"/>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
           <t>Cold weather pour complications</t>
@@ -3751,7 +4323,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Honeycombing in concrete</t>
@@ -3769,7 +4345,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n"/>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
           <t>Finish issues, surface defects</t>
@@ -3787,7 +4367,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Anchor bolts out of position</t>
@@ -3805,7 +4389,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n"/>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Waterproofing issues</t>
@@ -3823,7 +4411,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Drain tile or weeping tile problems</t>
@@ -3841,7 +4433,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Concrete pump truck issues</t>
@@ -3859,7 +4455,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Form failure during pour</t>
@@ -3877,7 +4477,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Settlement issues after pour</t>
@@ -3895,7 +4499,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Cracks in the slab</t>
@@ -3913,7 +4521,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Wrong rebar delivered or placed</t>
@@ -3931,7 +4543,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Major structural concern</t>
@@ -3949,7 +4565,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Footer below frost line issue</t>
@@ -3967,7 +4587,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Cold joint from delayed pour</t>
@@ -3985,7 +4609,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Honeycombing in foundation wall</t>
@@ -4003,7 +4631,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Bolts not where they need to be</t>
@@ -4021,7 +4653,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Water accumulating before pour</t>
@@ -4039,7 +4675,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Frost in ground, can't dig</t>
@@ -4057,7 +4697,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n"/>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Mix too wet, slump issue</t>
@@ -4075,7 +4719,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Truck running late</t>
@@ -4093,7 +4741,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
           <t>Pump issues on pour day</t>
@@ -4111,7 +4763,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Vapor barrier damaged</t>
@@ -4129,7 +4785,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n"/>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Grading not to spec</t>
@@ -4147,7 +4807,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Weather or ground conditions</t>
@@ -4165,7 +4829,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C39" s="18" t="n"/>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Forms still up, delaying next step</t>
@@ -4183,7 +4851,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n"/>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
           <t>General foundation defect</t>
@@ -4201,10 +4873,21 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C41" s="18" t="n"/>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Curing time or temperature issue</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -4212,6 +4895,11 @@
       <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Total entries: 40</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -4274,7 +4962,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Damaged, missing, or wrong trusses</t>
@@ -4292,7 +4984,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
           <t>Rafter issues, spacing, damage</t>
@@ -4310,7 +5006,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Floor or ceiling joist problems</t>
@@ -4328,7 +5028,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Stud spacing, damage, warping</t>
@@ -4346,7 +5050,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Beam placement, size, cracks</t>
@@ -4364,7 +5072,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Window/door header wrong size</t>
@@ -4382,7 +5094,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
           <t>OSB or plywood issues</t>
@@ -4400,7 +5116,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n"/>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Nail pattern, missing nails</t>
@@ -4418,7 +5138,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Joist hangers missing or wrong</t>
@@ -4436,7 +5160,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Ridge beam alignment</t>
@@ -4454,7 +5182,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Wall placement, square, plumb</t>
@@ -4472,7 +5204,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Corner framing, backing</t>
@@ -4490,7 +5226,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Missing fire blocking</t>
@@ -4508,7 +5248,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n"/>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
           <t>Truss web damage</t>
@@ -4526,7 +5270,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Notched studs or joists</t>
@@ -4544,7 +5292,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n"/>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
           <t>Oversized holes in framing</t>
@@ -4562,7 +5314,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Wall racking, out of square</t>
@@ -4580,7 +5336,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n"/>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Walls or posts not plumb</t>
@@ -4598,7 +5358,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Shear wall nailing or panel issues</t>
@@ -4616,7 +5380,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Holdown or strap missing</t>
@@ -4634,7 +5402,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Cracked truss member</t>
@@ -4652,7 +5424,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Broken truss during install</t>
@@ -4670,7 +5446,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Wall not square</t>
@@ -4688,7 +5468,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Ridge not aligned</t>
@@ -4706,7 +5490,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
           <t>OSB or plywood delaminating</t>
@@ -4724,7 +5512,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Hangers not installed</t>
@@ -4742,7 +5534,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Beam size wrong for span</t>
@@ -4760,7 +5556,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Load not transferred properly</t>
@@ -4778,7 +5578,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Wall leaning</t>
@@ -4796,7 +5600,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Too few nails, wrong spacing</t>
@@ -4814,7 +5622,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Web member failure</t>
@@ -4832,7 +5644,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n"/>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Header doesn't span opening</t>
@@ -4850,7 +5666,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Blocking not installed</t>
@@ -4868,7 +5688,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
           <t>Weather or crane issues</t>
@@ -4886,7 +5710,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Ridge sag, structural concern</t>
@@ -4904,7 +5732,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n"/>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Failed city/county inspection</t>
@@ -4922,7 +5754,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Shear panel fasteners incorrect</t>
@@ -4940,7 +5776,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C39" s="18" t="n"/>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Seismic tie-down missing</t>
@@ -4958,7 +5798,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n"/>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Wall out of plumb</t>
@@ -4976,10 +5820,21 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C41" s="18" t="n"/>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Splice plate undersized</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -4987,6 +5842,11 @@
       <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Total entries: 40</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -5049,7 +5909,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Vent pipe routing or size issues</t>
@@ -5067,7 +5931,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
           <t>Drain line slope or connection</t>
@@ -5085,7 +5953,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Pipe damage, wrong size</t>
@@ -5103,7 +5975,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
           <t>P-trap clearance or location</t>
@@ -5121,7 +5997,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Stub out location for fixtures</t>
@@ -5139,7 +6019,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Water meter location</t>
@@ -5157,7 +6041,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Sewer connection or cleanout</t>
@@ -5175,7 +6063,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n"/>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Gas piping issues</t>
@@ -5193,7 +6085,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Waste line problems</t>
@@ -5211,7 +6107,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Rough-in height or location</t>
@@ -5229,7 +6129,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Tub valve or drain location</t>
@@ -5247,7 +6151,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Shower pan or drain</t>
@@ -5265,7 +6173,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Toilet flange or rough spacing</t>
@@ -5283,7 +6195,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n"/>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
           <t>Sink drain or supply</t>
@@ -5301,7 +6217,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Missing or inaccessible cleanout</t>
@@ -5319,7 +6239,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n"/>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
           <t>Backwater valve missing</t>
@@ -5337,7 +6261,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Water pressure issues</t>
@@ -5355,7 +6283,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n"/>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Shutoff valve location or missing</t>
@@ -5373,7 +6305,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Leak at any plumbing connection</t>
@@ -5391,7 +6327,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Toilet flange height or damage</t>
@@ -5409,7 +6349,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Vent conflicts with framing</t>
@@ -5427,7 +6371,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Drain not sloped properly</t>
@@ -5445,7 +6393,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Fixture stub in wrong location</t>
@@ -5463,7 +6415,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Valve height off</t>
@@ -5481,7 +6437,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Drain not centered in shower pan</t>
@@ -5499,7 +6459,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Flange height above finish floor</t>
@@ -5517,7 +6481,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Cleanout not accessible</t>
@@ -5535,7 +6503,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Open gas line, safety issue</t>
@@ -5553,7 +6525,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
           <t>No cleanout at foundation exit</t>
@@ -5571,7 +6547,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Failed plumbing rough inspection</t>
@@ -5589,7 +6569,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Trap arm exceeds max length</t>
@@ -5607,7 +6591,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n"/>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Required but not installed</t>
@@ -5625,7 +6613,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Leak at joint or fitting</t>
@@ -5643,7 +6635,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
           <t>Missing hot water stub</t>
@@ -5661,7 +6657,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Pressure too high or low</t>
@@ -5679,7 +6679,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n"/>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Valve orientation wrong</t>
@@ -5697,7 +6701,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Flat waste line, will clog</t>
@@ -5715,7 +6723,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C39" s="18" t="n"/>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Supply line undersized</t>
@@ -5733,7 +6745,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n"/>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Framing not ready for plumbing</t>
@@ -5751,10 +6767,21 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C41" s="18" t="n"/>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Required floor drain not installed</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -5762,6 +6789,11 @@
       <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Total entries: 40</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -5824,7 +6856,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Ductwork size, routing, damage</t>
@@ -5842,7 +6878,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
           <t>Supply or return vent location</t>
@@ -5860,7 +6900,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Return air duct sizing</t>
@@ -5878,7 +6922,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Plenum box issues</t>
@@ -5896,7 +6944,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Register boot location</t>
@@ -5914,7 +6966,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Main trunk line issues</t>
@@ -5932,7 +6988,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Branch duct tap issues</t>
@@ -5950,7 +7010,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n"/>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Flex duct kinked or crushed</t>
@@ -5968,7 +7032,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Chase not framed correctly</t>
@@ -5986,7 +7054,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Condenser pad or location</t>
@@ -6004,7 +7076,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Furnace placement or clearance</t>
@@ -6022,7 +7098,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Flue pipe clearance issues</t>
@@ -6040,7 +7120,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Thermostat wire location</t>
@@ -6058,7 +7142,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n"/>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
           <t>Zoning damper issues</t>
@@ -6076,7 +7164,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Filter size or access issues</t>
@@ -6094,7 +7186,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n"/>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
           <t>Refrigerant line set routing</t>
@@ -6112,7 +7208,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Evaporator coil issues</t>
@@ -6130,7 +7230,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n"/>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Heat pump or furnace not heating</t>
@@ -6148,7 +7252,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
           <t>AC not cooling</t>
@@ -6166,7 +7274,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Condensate drain line issues</t>
@@ -6184,7 +7296,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Duct crushed during framing</t>
@@ -6202,7 +7318,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Kinked flex, airflow restricted</t>
@@ -6220,7 +7340,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Return undersized for unit</t>
@@ -6238,7 +7362,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Boot location conflicts with cabinet</t>
@@ -6256,7 +7384,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Duct leakage at seams</t>
@@ -6274,7 +7406,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Chase too small for duct</t>
@@ -6292,7 +7428,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Intake covered or obstructed</t>
@@ -6310,7 +7450,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Pad settling, unit not level</t>
@@ -6328,7 +7472,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Flue too close to combustibles</t>
@@ -6346,7 +7494,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Wire not run to location</t>
@@ -6364,7 +7516,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Damper stuck or wired wrong</t>
@@ -6382,7 +7538,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n"/>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Duct leakage test failure</t>
@@ -6400,7 +7560,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Clearance not to code</t>
@@ -6418,7 +7582,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
           <t>Refrigerant line damaged</t>
@@ -6436,7 +7604,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Electric not run yet</t>
@@ -6454,7 +7626,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n"/>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Can't change filter after build</t>
@@ -6472,7 +7648,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Duct disconnected at boot</t>
@@ -6490,7 +7670,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C39" s="18" t="n"/>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Drain line blocked, water risk</t>
@@ -6508,7 +7692,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n"/>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
           <t>AC not working</t>
@@ -6526,10 +7714,21 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C41" s="18" t="n"/>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Framing not ready for HVAC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -6537,6 +7736,11 @@
       <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Total entries: 40</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -6599,7 +7803,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Wire gauge, type, or damage</t>
@@ -6617,7 +7825,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
           <t>Romex stapling, damage violations</t>
@@ -6635,7 +7847,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Box fill, placement, missing</t>
@@ -6653,7 +7869,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Switch location or height</t>
@@ -6671,7 +7891,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Outlet spacing or location</t>
@@ -6689,7 +7913,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Receptacle type or placement</t>
@@ -6707,7 +7935,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Conduit fill, routing, damage</t>
@@ -6725,7 +7957,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n"/>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Panel location, clearance</t>
@@ -6743,7 +7979,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Breaker sizing or trip issues</t>
@@ -6761,7 +8001,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Missing or improper ground</t>
@@ -6779,7 +8023,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
           <t>AFCI breaker requirements</t>
@@ -6797,7 +8045,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
           <t>GFCI protection missing</t>
@@ -6815,7 +8067,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Smoke detector location, wiring</t>
@@ -6833,7 +8089,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n"/>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
           <t>Stapling too tight, spacing</t>
@@ -6851,7 +8111,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Missing nail plates on studs</t>
@@ -6869,7 +8133,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n"/>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
           <t>Oversized holes in joists/studs</t>
@@ -6887,7 +8155,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Junction box accessibility</t>
@@ -6905,7 +8177,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n"/>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Meter can location or damage</t>
@@ -6923,7 +8199,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Missing home run to panel</t>
@@ -6941,7 +8221,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Improper splice in junction box</t>
@@ -6959,7 +8243,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Undersized for circuit</t>
@@ -6977,7 +8265,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Box doesn't line up with layout</t>
@@ -6995,7 +8287,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Not ADA or spec height</t>
@@ -7013,7 +8309,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Ungrounded circuit</t>
@@ -7031,7 +8331,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Wire at risk of nail puncture</t>
@@ -7049,7 +8353,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Oversized holes in framing</t>
@@ -7067,7 +8375,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Loose wire, code violation</t>
@@ -7085,7 +8397,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Not interconnected</t>
@@ -7103,7 +8419,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Panel space not to code</t>
@@ -7121,7 +8441,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Required but not installed</t>
@@ -7139,7 +8463,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Framing/walls not ready</t>
@@ -7157,7 +8485,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n"/>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Failed electrical inspection</t>
@@ -7175,7 +8507,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
           <t>J-box not accessible</t>
@@ -7193,7 +8529,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
           <t>Conduit fill over max</t>
@@ -7211,7 +8551,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Something is shorting</t>
@@ -7229,7 +8573,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n"/>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Utility not connected</t>
@@ -7247,7 +8595,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Meter socket damaged</t>
@@ -7265,7 +8617,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C39" s="18" t="n"/>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Missing home run to panel</t>
@@ -7283,7 +8639,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n"/>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
           <t>AFCI not installed</t>
@@ -7301,10 +8661,21 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C41" s="18" t="n"/>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Box not rated for ceiling fan</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -7312,6 +8683,11 @@
       <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Total entries: 40</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -7374,7 +8750,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Joint compound, drying, finish</t>
@@ -7392,7 +8772,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
           <t>Tape bubbling, lifting, cracking</t>
@@ -7410,7 +8794,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Corner bead loose or damaged</t>
@@ -7428,7 +8816,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Screw pops, missed, or depth</t>
@@ -7446,7 +8838,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Nail pops</t>
@@ -7464,7 +8860,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Joint finishing, cracking</t>
@@ -7482,7 +8882,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Corner issues, inside/outside</t>
@@ -7500,7 +8904,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n"/>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Ceiling sag, seam issues</t>
@@ -7518,7 +8926,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Texture matching, orange peel</t>
@@ -7536,7 +8948,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Sanding dust, finish quality</t>
@@ -7554,7 +8970,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Patch work needed</t>
@@ -7572,7 +8992,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Cracks in drywall</t>
@@ -7590,7 +9014,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Bump at joint or repair</t>
@@ -7608,7 +9036,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n"/>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
           <t>Wall or ceiling bowing</t>
@@ -7626,7 +9058,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Hump at tapered joint</t>
@@ -7644,7 +9080,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n"/>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
           <t>Gap at base of wall</t>
@@ -7662,7 +9102,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Rust spots from exposed nails</t>
@@ -7680,7 +9124,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n"/>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Screw or nail pop</t>
@@ -7698,7 +9146,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Floating or skim coat issues</t>
@@ -7716,7 +9168,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Fire-rated drywall or tape issues</t>
@@ -7734,7 +9190,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Tape not bedded properly</t>
@@ -7752,7 +9212,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Bead not nailed properly</t>
@@ -7770,7 +9234,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Too many exposed screw heads</t>
@@ -7788,7 +9256,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Ceiling board not supported</t>
@@ -7806,7 +9278,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Tapered joint cracks</t>
@@ -7824,7 +9300,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Patch texture different</t>
@@ -7842,7 +9322,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Can't sand or paint</t>
@@ -7860,7 +9344,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Cracks at ceiling joints</t>
@@ -7878,7 +9366,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Wall needs skim coat</t>
@@ -7896,7 +9388,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Corner finish not smooth</t>
@@ -7914,7 +9410,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Gap at bottom of wall</t>
@@ -7932,7 +9432,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n"/>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Rust spots bleeding through</t>
@@ -7950,7 +9454,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Water damage to installed board</t>
@@ -7968,7 +9476,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
           <t>Rough trades not finished</t>
@@ -7986,7 +9498,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Board not straight</t>
@@ -8004,7 +9520,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n"/>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Fire-rated wall tape not done</t>
@@ -8022,7 +9542,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Dust covering job site</t>
@@ -8040,7 +9564,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C39" s="18" t="n"/>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Crushed or broken corner</t>
@@ -8058,7 +9586,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n"/>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Tape joint failed, needs redo</t>
@@ -8076,10 +9608,21 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C41" s="18" t="n"/>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Screw not catching in stud</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -8087,6 +9630,11 @@
       <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Total entries: 40</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
@@ -8149,7 +9697,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C2" s="5" t="n"/>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D2" s="16" t="inlineStr">
         <is>
           <t>Wall paint coverage or issues</t>
@@ -8167,7 +9719,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C3" s="18" t="n"/>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
           <t>Ceiling paint, flashing</t>
@@ -8185,7 +9741,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C4" s="5" t="n"/>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D4" s="16" t="inlineStr">
         <is>
           <t>Trim paint, brush marks, drips</t>
@@ -8203,7 +9763,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C5" s="18" t="n"/>
+      <c r="C5" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
           <t>Door paint, finish quality</t>
@@ -8221,7 +9785,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C6" s="5" t="n"/>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
           <t>Cabinet paint or color issues</t>
@@ -8239,7 +9807,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C7" s="18" t="n"/>
+      <c r="C7" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
           <t>Stain color or application</t>
@@ -8257,7 +9829,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C8" s="5" t="n"/>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
           <t>Primer not applied or wrong type</t>
@@ -8275,7 +9851,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C9" s="18" t="n"/>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
           <t>Number of coats, coverage</t>
@@ -8293,7 +9873,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C10" s="5" t="n"/>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
           <t>Shiny spots from touch-up</t>
@@ -8311,7 +9895,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C11" s="18" t="n"/>
+      <c r="C11" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D11" s="19" t="inlineStr">
         <is>
           <t>Paint drips on trim or floor</t>
@@ -8329,7 +9917,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C12" s="5" t="n"/>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D12" s="16" t="inlineStr">
         <is>
           <t>Roller marks or texture</t>
@@ -8347,7 +9939,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C13" s="18" t="n"/>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D13" s="19" t="inlineStr">
         <is>
           <t>Brush marks visible</t>
@@ -8365,7 +9961,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C14" s="5" t="n"/>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D14" s="16" t="inlineStr">
         <is>
           <t>Caulk gap at trim</t>
@@ -8383,7 +9983,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C15" s="18" t="n"/>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D15" s="19" t="inlineStr">
         <is>
           <t>Caulking cracking or missing</t>
@@ -8401,7 +10005,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C16" s="5" t="n"/>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D16" s="16" t="inlineStr">
         <is>
           <t>Sheen mismatch</t>
@@ -8419,7 +10027,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C17" s="18" t="n"/>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D17" s="19" t="inlineStr">
         <is>
           <t>Patched area not primed</t>
@@ -8437,7 +10049,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C18" s="5" t="n"/>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D18" s="16" t="inlineStr">
         <is>
           <t>Paint spray reaching adjacent areas</t>
@@ -8455,7 +10071,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C19" s="18" t="n"/>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D19" s="19" t="inlineStr">
         <is>
           <t>Paint peeling or adhesion failure</t>
@@ -8473,7 +10093,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C20" s="5" t="n"/>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D20" s="16" t="inlineStr">
         <is>
           <t>Paint bleeding under tape</t>
@@ -8491,7 +10115,11 @@
           <t>Word</t>
         </is>
       </c>
-      <c r="C21" s="18" t="n"/>
+      <c r="C21" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D21" s="19" t="inlineStr">
         <is>
           <t>Final touch-up not done</t>
@@ -8509,7 +10137,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C22" s="5" t="n"/>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D22" s="16" t="inlineStr">
         <is>
           <t>Coverage not sufficient</t>
@@ -8527,7 +10159,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C23" s="18" t="n"/>
+      <c r="C23" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D23" s="19" t="inlineStr">
         <is>
           <t>Shiny spots on ceiling</t>
@@ -8545,7 +10181,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C24" s="5" t="n"/>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D24" s="16" t="inlineStr">
         <is>
           <t>Visible brush strokes</t>
@@ -8563,7 +10203,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C25" s="18" t="n"/>
+      <c r="C25" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D25" s="19" t="inlineStr">
         <is>
           <t>Adhesion failure</t>
@@ -8581,7 +10225,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C26" s="5" t="n"/>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D26" s="16" t="inlineStr">
         <is>
           <t>Caulk failed at joints</t>
@@ -8599,7 +10247,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C27" s="18" t="n"/>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D27" s="19" t="inlineStr">
         <is>
           <t>Touch-up paint different shade</t>
@@ -8617,7 +10269,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C28" s="5" t="n"/>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D28" s="16" t="inlineStr">
         <is>
           <t>Eggshell vs flat mismatch</t>
@@ -8635,7 +10291,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C29" s="18" t="n"/>
+      <c r="C29" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D29" s="19" t="inlineStr">
         <is>
           <t>Paint droplets on flooring</t>
@@ -8653,7 +10313,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C30" s="5" t="n"/>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D30" s="16" t="inlineStr">
         <is>
           <t>Runs or sags on doors</t>
@@ -8671,7 +10335,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C31" s="18" t="n"/>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D31" s="19" t="inlineStr">
         <is>
           <t>Stain uneven absorption</t>
@@ -8689,7 +10357,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C32" s="5" t="n"/>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D32" s="16" t="inlineStr">
         <is>
           <t>Patch flashing through paint</t>
@@ -8707,7 +10379,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C33" s="18" t="n"/>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D33" s="19" t="inlineStr">
         <is>
           <t>Tape line not crisp</t>
@@ -8725,7 +10401,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C34" s="5" t="n"/>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D34" s="16" t="inlineStr">
         <is>
           <t>Orange peel vs smooth mismatch</t>
@@ -8743,7 +10423,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C35" s="18" t="n"/>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D35" s="19" t="inlineStr">
         <is>
           <t>Joints visible after painting</t>
@@ -8761,7 +10445,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C36" s="5" t="n"/>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D36" s="16" t="inlineStr">
         <is>
           <t>Full repaint needed</t>
@@ -8779,7 +10467,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C37" s="18" t="n"/>
+      <c r="C37" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D37" s="19" t="inlineStr">
         <is>
           <t>Drywall not ready</t>
@@ -8797,7 +10489,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C38" s="5" t="n"/>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D38" s="16" t="inlineStr">
         <is>
           <t>Exterior paint failing</t>
@@ -8815,7 +10511,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C39" s="18" t="n"/>
+      <c r="C39" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D39" s="19" t="inlineStr">
         <is>
           <t>Missed scope item</t>
@@ -8833,7 +10533,11 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C40" s="5" t="n"/>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>Red</t>
+        </is>
+      </c>
       <c r="D40" s="16" t="inlineStr">
         <is>
           <t>Final touch-up walk not complete</t>
@@ -8851,10 +10555,21 @@
           <t>Phrase</t>
         </is>
       </c>
-      <c r="C41" s="18" t="n"/>
+      <c r="C41" s="18" t="inlineStr">
+        <is>
+          <t>Yellow</t>
+        </is>
+      </c>
       <c r="D41" s="19" t="inlineStr">
         <is>
           <t>Missed scope item</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Red</t>
         </is>
       </c>
     </row>
@@ -8862,6 +10577,11 @@
       <c r="A43" s="20" t="inlineStr">
         <is>
           <t>Total entries: 40</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Yellow</t>
         </is>
       </c>
     </row>
